--- a/24_DS_Gen_Ahm_1/01_Advanced Excel/sep20.xlsx
+++ b/24_DS_Gen_Ahm_1/01_Advanced Excel/sep20.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alakh Pandya\Desktop\Batches\24_DS_Gen_Ahm_1\Advanced Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alakh Pandya\Desktop\all_batches\24_DS_Gen_Ahm_1\01_Advanced Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99AEA1B8-5A09-4B63-9554-DA718C998681}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3224CE2-4BE5-4BB6-A0BA-CC05F4914150}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{65B08B18-C9BC-4687-A3BE-1994E4BC8EA6}"/>
   </bookViews>
@@ -589,6 +589,10 @@
       <c r="L2" t="s">
         <v>26</v>
       </c>
+      <c r="M2">
+        <f>IF(I2="Yes", $G$2+H2, H2)</f>
+        <v>65</v>
+      </c>
       <c r="N2" s="1">
         <f>SUM(J:J)</f>
         <v>9</v>
@@ -613,11 +617,15 @@
         <v>68</v>
       </c>
       <c r="I3" t="str">
-        <f t="shared" ref="I3:I22" si="2">IF(H3&gt;=50, "Yes", "No")</f>
+        <f t="shared" ref="I3:I15" si="2">IF(H3&gt;=50, "Yes", "No")</f>
         <v>Yes</v>
       </c>
       <c r="L3" t="s">
         <v>8</v>
+      </c>
+      <c r="M3">
+        <f t="shared" ref="M3:M15" si="3">IF(I3="Yes", $G$2+H3, H3)</f>
+        <v>78</v>
       </c>
       <c r="N3" s="1" t="s">
         <v>9</v>
@@ -651,6 +659,10 @@
       <c r="L4" t="s">
         <v>26</v>
       </c>
+      <c r="M4">
+        <f t="shared" si="3"/>
+        <v>87</v>
+      </c>
       <c r="N4" s="1">
         <f>COUNT(C2:C15)</f>
         <v>11</v>
@@ -684,6 +696,10 @@
       <c r="L5" t="s">
         <v>26</v>
       </c>
+      <c r="M5">
+        <f t="shared" si="3"/>
+        <v>108</v>
+      </c>
       <c r="N5" s="1" t="s">
         <v>10</v>
       </c>
@@ -722,6 +738,10 @@
       <c r="L6" t="s">
         <v>8</v>
       </c>
+      <c r="M6">
+        <f t="shared" si="3"/>
+        <v>93</v>
+      </c>
       <c r="N6" s="1">
         <f>COUNT(B2:B15)</f>
         <v>10</v>
@@ -758,6 +778,10 @@
       <c r="L7" t="s">
         <v>8</v>
       </c>
+      <c r="M7">
+        <f t="shared" si="3"/>
+        <v>102</v>
+      </c>
       <c r="N7" s="1"/>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
@@ -791,6 +815,10 @@
       <c r="L8" t="s">
         <v>8</v>
       </c>
+      <c r="M8">
+        <f t="shared" si="3"/>
+        <v>62</v>
+      </c>
       <c r="N8" s="1" t="s">
         <v>11</v>
       </c>
@@ -820,6 +848,10 @@
       <c r="L9" t="s">
         <v>26</v>
       </c>
+      <c r="M9">
+        <f t="shared" si="3"/>
+        <v>33</v>
+      </c>
       <c r="N9" s="1">
         <f>COUNTA(K2:K15)</f>
         <v>8</v>
@@ -859,6 +891,10 @@
       <c r="L10" t="s">
         <v>26</v>
       </c>
+      <c r="M10">
+        <f t="shared" si="3"/>
+        <v>8</v>
+      </c>
       <c r="N10" s="1" t="s">
         <v>12</v>
       </c>
@@ -891,6 +927,10 @@
       <c r="L11" t="s">
         <v>8</v>
       </c>
+      <c r="M11">
+        <f t="shared" si="3"/>
+        <v>42</v>
+      </c>
       <c r="N11" s="1">
         <f>COUNTIF(H:H, "&gt;=70")</f>
         <v>6</v>
@@ -924,6 +964,10 @@
       <c r="L12" t="s">
         <v>26</v>
       </c>
+      <c r="M12">
+        <f t="shared" si="3"/>
+        <v>49</v>
+      </c>
       <c r="N12" s="1" t="s">
         <v>13</v>
       </c>
@@ -959,6 +1003,10 @@
       <c r="L13" t="s">
         <v>8</v>
       </c>
+      <c r="M13">
+        <f t="shared" si="3"/>
+        <v>39</v>
+      </c>
       <c r="N13" s="1">
         <f>COUNTIF(H:H, 8)</f>
         <v>1</v>
@@ -995,6 +1043,10 @@
       <c r="L14" t="s">
         <v>26</v>
       </c>
+      <c r="M14">
+        <f t="shared" si="3"/>
+        <v>100</v>
+      </c>
       <c r="N14" s="2" t="s">
         <v>27</v>
       </c>
@@ -1032,6 +1084,10 @@
       </c>
       <c r="L15" t="s">
         <v>8</v>
+      </c>
+      <c r="M15">
+        <f t="shared" si="3"/>
+        <v>90</v>
       </c>
       <c r="N15" s="2">
         <f>COUNTIF(L:L, "P")</f>
